--- a/separationIG/ig/all-profiles.xlsx
+++ b/separationIG/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T12:59:35+00:00</t>
+    <t>2026-09-29T13:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
